--- a/QR Code/PC's Sheet.csv.xlsx
+++ b/QR Code/PC's Sheet.csv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programes\Projects\QR Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B498E969-2DE5-4DA8-A95E-C9F3B34AEEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3845379B-560A-4DCF-8E68-BC0914BC8C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F0D21D7-3A5A-40E1-94D5-58902FAE4869}"/>
   </bookViews>
@@ -1078,7 +1078,7 @@
   <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="12" max="12" width="215.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="136.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1142,8 +1142,8 @@
         <v>0</v>
       </c>
       <c r="L2" t="str">
-        <f>"https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=" &amp; A2</f>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=1</v>
+        <f>"https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=" &amp; A2</f>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=1</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1175,8 +1175,8 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <f t="shared" ref="L3:L19" si="0">"https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=" &amp; A3</f>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=2</v>
+        <f t="shared" ref="L3:L19" si="0">"https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=" &amp; A3</f>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=2</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="L4" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=3</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=3</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L5" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=4</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=4</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="L6" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=5</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=5</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L7" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=6</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=6</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="L8" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=7</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=7</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L9" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=8</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=8</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="L10" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=9</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=9</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="L11" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=10</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=10</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="L12" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=11</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=11</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="L13" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=12</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=12</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=13</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=13</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="L15" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=14</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=14</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="L16" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=15</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=15</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="L17" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=16</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=16</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L18" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=17</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=17</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="L19" t="str">
         <f t="shared" si="0"/>
-        <v>https://samafinance-my.sharepoint.com/:u:/p/ahmed_ibrahim/IQBXv309mXl-R6_heQHmesDMAeg7p-BFulE_nfbzRtwcKbg?e=qbydQP/index.html?id=18</v>
+        <v>https://github.com/AhmedIbrahim000/qr-devices/blob/main/QR%20Code/index.html?id=18</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
